--- a/static/teaching/ProductionFiguresWeb.xlsx
+++ b/static/teaching/ProductionFiguresWeb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\JonPrivate\Textbook\CH2 Production\FiguresTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{544E95C8-B4A3-4031-BCE7-1E76DC59B499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08B810F8-E7DF-40B8-8BF9-DA96283D2A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{5A49139F-7635-4795-BC14-E0254E57C157}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{5A49139F-7635-4795-BC14-E0254E57C157}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
   <si>
     <t>Labor Share in the United States, 1947-2024</t>
   </si>
@@ -5765,55 +5765,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0.57819235324859619</c:v>
+                  <c:v>57.819235324859619</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.46236312389373779</c:v>
+                  <c:v>46.236312389373779</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5239112377166748</c:v>
+                  <c:v>52.39112377166748</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.47245791554450989</c:v>
+                  <c:v>47.245791554450989</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.45154058933258057</c:v>
+                  <c:v>45.154058933258057</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.36750513315200806</c:v>
+                  <c:v>36.750513315200806</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.32173064351081848</c:v>
+                  <c:v>32.173064351081848</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.26041856408119202</c:v>
+                  <c:v>26.041856408119202</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.18229062855243683</c:v>
+                  <c:v>18.229062855243683</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.12103493511676788</c:v>
+                  <c:v>12.103493511676788</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.7470505833625793E-2</c:v>
+                  <c:v>6.7470505833625793</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.6652974784374237E-2</c:v>
+                  <c:v>3.6652974784374237</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.9561722651124001E-2</c:v>
+                  <c:v>2.9561722651124001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.709398977458477E-2</c:v>
+                  <c:v>2.709398977458477</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.2298421710729599E-2</c:v>
+                  <c:v>2.2298421710729599</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.4275433272123337E-2</c:v>
+                  <c:v>2.4275433272123337</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.356322854757309E-2</c:v>
+                  <c:v>2.356322854757309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5852,55 +5852,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0.1424071416258812</c:v>
+                  <c:v>14.24071416258812</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12460075318813324</c:v>
+                  <c:v>12.460075318813324</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1188003271818161</c:v>
+                  <c:v>11.88003271818161</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.13454792648553848</c:v>
+                  <c:v>13.454792648553848</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.12653639540076256</c:v>
+                  <c:v>12.653639540076256</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.15954935550689697</c:v>
+                  <c:v>15.954935550689697</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.19586332142353058</c:v>
+                  <c:v>19.586332142353058</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.18549373000860214</c:v>
+                  <c:v>18.549373000860214</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.22812043130397797</c:v>
+                  <c:v>22.812043130397797</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.26098918914794922</c:v>
+                  <c:v>26.098918914794922</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.27694908529520035</c:v>
+                  <c:v>27.694908529520035</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.25373708456754684</c:v>
+                  <c:v>25.373708456754684</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.22359887510538101</c:v>
+                  <c:v>22.359887510538101</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.17522423714399338</c:v>
+                  <c:v>17.522423714399338</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.14607533812522888</c:v>
+                  <c:v>14.607533812522888</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.10870356112718582</c:v>
+                  <c:v>10.870356112718582</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.10112689808011055</c:v>
+                  <c:v>10.112689808011055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5938,55 +5938,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>3.0806227819994092E-2</c:v>
+                  <c:v>3.0806227819994092</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3096759589388967E-2</c:v>
+                  <c:v>4.3096759589388967</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.557201474905014E-2</c:v>
+                  <c:v>3.557201474905014</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3060583062469959E-2</c:v>
+                  <c:v>4.3060583062469959</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.3830679506063461E-2</c:v>
+                  <c:v>5.3830679506063461</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.753682367503643E-2</c:v>
+                  <c:v>5.753682367503643</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.8761678412556648E-2</c:v>
+                  <c:v>6.8761678412556648</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.6167623996734619E-2</c:v>
+                  <c:v>9.6167623996734619</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.10242199897766113</c:v>
+                  <c:v>10.242199897766113</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1142464391887188</c:v>
+                  <c:v>11.42464391887188</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1542033813893795</c:v>
+                  <c:v>15.42033813893795</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.21276897564530373</c:v>
+                  <c:v>21.276897564530373</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.24769829958677292</c:v>
+                  <c:v>24.769829958677292</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.27523360401391983</c:v>
+                  <c:v>27.523360401391983</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.30081237852573395</c:v>
+                  <c:v>30.081237852573395</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.33181862533092499</c:v>
+                  <c:v>33.181862533092499</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.33758381009101868</c:v>
+                  <c:v>33.758381009101868</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10733,7 +10733,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
+      <xdr:colOff>107950</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>50482</xdr:rowOff>
     </xdr:to>
@@ -11122,170 +11122,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E10CD8-73F2-48D6-B3B6-BE779BB1C990}">
   <dimension ref="A2:A46"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>72</v>
       </c>
@@ -11299,32 +11299,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEBF069E-E1AE-4011-A318-A1561842ECEB}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1947</v>
       </c>
@@ -11336,7 +11336,7 @@
         <v>61.232051282051266</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1948</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1949</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1950</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1951</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1952</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1953</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1954</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1955</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1956</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1957</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1958</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1959</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1960</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>1961</v>
       </c>
@@ -11456,7 +11456,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1962</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>1963</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>1964</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>1965</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>1966</v>
       </c>
@@ -11496,7 +11496,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>1967</v>
       </c>
@@ -11504,7 +11504,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>1968</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>1969</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>1970</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>1971</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>1972</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>1973</v>
       </c>
@@ -11552,7 +11552,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>1974</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>1975</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>1976</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>1977</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>1978</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>1979</v>
       </c>
@@ -11600,7 +11600,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>1980</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>63.3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>1981</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>1982</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>1983</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>61.7</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>1984</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>1985</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>1986</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>1987</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>1988</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>1989</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>62.1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>1990</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>1991</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>1992</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>1993</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>1994</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>1995</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>1996</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1997</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>1998</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>1999</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>2000</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>2001</v>
       </c>
@@ -11776,7 +11776,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>2002</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>2003</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>2004</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>2005</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>2006</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>2007</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>2008</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>59.4</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>2009</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>2010</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>2011</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>56.3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>2012</v>
       </c>
@@ -11864,7 +11864,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>2013</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>2014</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>2015</v>
       </c>
@@ -11888,7 +11888,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>2016</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>2017</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>2018</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>2019</v>
       </c>
@@ -11920,7 +11920,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>2020</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>2021</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>56.8</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>2022</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>2023</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>2024</v>
       </c>
@@ -11970,12 +11970,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A195DCA3-DC42-4276-BC72-1D578F45A75F}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1900</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>21.532</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1905</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>22.077000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1910</v>
       </c>
@@ -12019,7 +12019,7 @@
         <v>24.042999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1915</v>
       </c>
@@ -12031,7 +12031,7 @@
         <v>26.492999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1920</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1925</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>22.082000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1930</v>
       </c>
@@ -12067,7 +12067,7 @@
         <v>18.885999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1935</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>16.675999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1940</v>
       </c>
@@ -12091,7 +12091,7 @@
         <v>13.932</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1945</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>11.629</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1950</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>7.6040000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1955</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>4.3090000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1960</v>
       </c>
@@ -12152,9 +12152,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10106EA5-A649-4ADE-8813-6EE32555EEE9}">
   <dimension ref="A1:E91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>1929</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>0.67563766241073608</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>1930</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>0.67561548948287964</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>1931</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>0.67559331655502319</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>1932</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>0.67557114362716675</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>1933</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>0.67554891109466553</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>1934</v>
       </c>
@@ -12273,7 +12273,7 @@
         <v>0.67552673816680908</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>1935</v>
       </c>
@@ -12290,7 +12290,7 @@
         <v>0.67550456523895264</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>1936</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>0.67548239231109619</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>1937</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>0.67546021938323975</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>1938</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>0.6754380464553833</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>1939</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>0.67541587352752686</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>1940</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>0.67539370059967041</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>1941</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>0.67537152767181396</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>1942</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>0.67534929513931274</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>1943</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>0.6753271222114563</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>1944</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>0.67530494928359985</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>1945</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>0.67528277635574341</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>1946</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>0.67526060342788696</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>1947</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>0.67523843050003052</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>1948</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>0.67521625757217407</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>1949</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>0.67519408464431763</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>1950</v>
       </c>
@@ -12545,7 +12545,7 @@
         <v>0.67517185211181641</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>1951</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>0.67514967918395996</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>1952</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>0.67512750625610352</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>1953</v>
       </c>
@@ -12596,7 +12596,7 @@
         <v>0.67510533332824707</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>1954</v>
       </c>
@@ -12613,7 +12613,7 @@
         <v>0.67508316040039063</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>1955</v>
       </c>
@@ -12630,7 +12630,7 @@
         <v>0.67506098747253418</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>1956</v>
       </c>
@@ -12647,7 +12647,7 @@
         <v>0.67503881454467773</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>1957</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>0.67501664161682129</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>1958</v>
       </c>
@@ -12681,7 +12681,7 @@
         <v>0.67499446868896484</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>1959</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>0.67497223615646362</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>1960</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>0.67495006322860718</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>1961</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>0.67492789030075073</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>1962</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>0.67490571737289429</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>1963</v>
       </c>
@@ -12766,7 +12766,7 @@
         <v>0.67488354444503784</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>1964</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>0.6748613715171814</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>1965</v>
       </c>
@@ -12800,7 +12800,7 @@
         <v>0.67483919858932495</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>1966</v>
       </c>
@@ -12817,7 +12817,7 @@
         <v>0.67481702566146851</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>1967</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>0.67479485273361206</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>1968</v>
       </c>
@@ -12851,7 +12851,7 @@
         <v>0.67477262020111084</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>1969</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>0.67475044727325439</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>1970</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>0.67472827434539795</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>1971</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>0.6747061014175415</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>1972</v>
       </c>
@@ -12919,7 +12919,7 @@
         <v>0.67468392848968506</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>1973</v>
       </c>
@@ -12936,7 +12936,7 @@
         <v>0.67466175556182861</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>1974</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>0.67463958263397217</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>1975</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>0.67461740970611572</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>1976</v>
       </c>
@@ -12987,7 +12987,7 @@
         <v>0.6745951771736145</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>1977</v>
       </c>
@@ -13004,7 +13004,7 @@
         <v>0.67457300424575806</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>1978</v>
       </c>
@@ -13021,7 +13021,7 @@
         <v>0.67455083131790161</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>1979</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>0.67452865839004517</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>1980</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>0.67450648546218872</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>1981</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>0.67448431253433228</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>1982</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>0.67446213960647583</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>1983</v>
       </c>
@@ -13106,7 +13106,7 @@
         <v>0.67443996667861938</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>1984</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>0.67441779375076294</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>1985</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>0.67439556121826172</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>1986</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>0.67437338829040527</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>1987</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>0.67435121536254883</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>1988</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>0.67432904243469238</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>1989</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>0.67430686950683594</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>1990</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>0.67428469657897949</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>1991</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>0.67426252365112305</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>1992</v>
       </c>
@@ -13259,7 +13259,7 @@
         <v>0.6742403507232666</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>1993</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>0.67421817779541016</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>1994</v>
       </c>
@@ -13293,7 +13293,7 @@
         <v>0.67419594526290894</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>1995</v>
       </c>
@@ -13310,7 +13310,7 @@
         <v>0.67417377233505249</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>1996</v>
       </c>
@@ -13327,7 +13327,7 @@
         <v>0.67415159940719604</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>1997</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>0.6741294264793396</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>1998</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>0.67410725355148315</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>1999</v>
       </c>
@@ -13378,7 +13378,7 @@
         <v>0.67408508062362671</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>2000</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>0.67406290769577026</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>2001</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>0.67404073476791382</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>2002</v>
       </c>
@@ -13429,7 +13429,7 @@
         <v>0.6740185022354126</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>2003</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>0.67399632930755615</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>2004</v>
       </c>
@@ -13463,7 +13463,7 @@
         <v>0.67397415637969971</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>2005</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>0.67395198345184326</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>2006</v>
       </c>
@@ -13497,7 +13497,7 @@
         <v>0.67392981052398682</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>2007</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>0.67390763759613037</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>2008</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>0.67388546466827393</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>2009</v>
       </c>
@@ -13548,7 +13548,7 @@
         <v>0.67386329174041748</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>2010</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>0.67384111881256104</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
         <v>2011</v>
       </c>
@@ -13582,7 +13582,7 @@
         <v>0.67381888628005981</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>2012</v>
       </c>
@@ -13599,7 +13599,7 @@
         <v>0.67379671335220337</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>2013</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>0.67377454042434692</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>2014</v>
       </c>
@@ -13633,7 +13633,7 @@
         <v>0.67375236749649048</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>2015</v>
       </c>
@@ -13650,7 +13650,7 @@
         <v>0.67373019456863403</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>2016</v>
       </c>
@@ -13667,7 +13667,7 @@
         <v>0.67370802164077759</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>2017</v>
       </c>
@@ -13684,7 +13684,7 @@
         <v>0.67368584871292114</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>2018</v>
       </c>
@@ -13710,9 +13710,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4597E41E-F41A-40F5-9813-B405E42B42CE}">
   <dimension ref="A1:E79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -13729,7 +13729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1947</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>0.97520658187603326</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1948</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>0.99788279049945616</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1949</v>
       </c>
@@ -13783,7 +13783,7 @@
         <v>1.0107200298671803</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1950</v>
       </c>
@@ -13801,7 +13801,7 @@
         <v>1.021852168617281</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1951</v>
       </c>
@@ -13819,7 +13819,7 @@
         <v>1.0422151794795209</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1952</v>
       </c>
@@ -13837,7 +13837,7 @@
         <v>1.038324582894594</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1953</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>1.0283769029542067</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1954</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>1.0249426124946075</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1955</v>
       </c>
@@ -13891,7 +13891,7 @@
         <v>1.0255535521041881</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1956</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>1.0483287406192878</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1957</v>
       </c>
@@ -13927,7 +13927,7 @@
         <v>1.0466033809637394</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1958</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>1.0262383560571726</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1959</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>1.0224543512336697</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1960</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>1.0144863046756505</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1961</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>1.0018757342507121</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1962</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>0.99091945873732123</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1963</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>0.97706200446377323</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1964</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>0.96859619264156027</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1965</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>0.96587845382632997</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1966</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>0.95874045683921394</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1967</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>0.95559232506549319</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1968</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>0.95103879890139931</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1969</v>
       </c>
@@ -14143,7 +14143,7 @@
         <v>0.94996870022678703</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1970</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>0.94119847366931009</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1971</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>0.94008584832898456</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1972</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>0.93870523240990356</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1973</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>0.93847320723020156</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1974</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>0.94709229323054422</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1975</v>
       </c>
@@ -14251,7 +14251,7 @@
         <v>0.97044761940302415</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1976</v>
       </c>
@@ -14269,7 +14269,7 @@
         <v>0.97063444067231774</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1977</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>0.98122778350491591</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1978</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>0.99104440949459027</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1979</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>0.99727230222218088</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1980</v>
       </c>
@@ -14341,7 +14341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1981</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>0.99899307751962907</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1982</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>0.99068779227521786</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1983</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>0.95633486120010114</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1984</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>0.93294809965057757</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1985</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>0.9155393660488661</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1986</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>0.91752710321093667</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1987</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>0.91413566920973433</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1988</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>0.90515919515925081</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1989</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>0.8932081812677285</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1990</v>
       </c>
@@ -14521,7 +14521,7 @@
         <v>0.87884528001410778</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1991</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>0.86464482746051874</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1992</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>0.84536645121787812</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1993</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>0.83555799442736645</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1994</v>
       </c>
@@ -14593,7 +14593,7 @@
         <v>0.83032666299303171</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1995</v>
       </c>
@@ -14611,7 +14611,7 @@
         <v>0.82634899549004903</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1996</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>0.81105014067221259</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1997</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>0.79769844837727999</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1998</v>
       </c>
@@ -14665,7 +14665,7 @@
         <v>0.7831962126670714</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1999</v>
       </c>
@@ -14683,7 +14683,7 @@
         <v>0.77311008500565892</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2000</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>0.76574163886910429</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2001</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>0.75486836836966353</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2002</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>0.74615493707327674</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2003</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>0.73751157010428303</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2004</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>0.73930677577377402</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2005</v>
       </c>
@@ -14791,7 +14791,7 @@
         <v>0.74593252480475225</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2006</v>
       </c>
@@ -14809,7 +14809,7 @@
         <v>0.74887238847725612</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2007</v>
       </c>
@@ -14827,7 +14827,7 @@
         <v>0.74011621184547072</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2008</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>0.73240984601215686</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2009</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>0.71928768031577595</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2010</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>0.69877121917453744</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2011</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>0.69130318273232305</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2012</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>0.68721738090970086</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2013</v>
       </c>
@@ -14935,7 +14935,7 @@
         <v>0.68175722612974488</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2014</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>0.68154973960482867</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2015</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>0.67838534808226236</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2016</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>0.67073604179398383</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2017</v>
       </c>
@@ -15007,7 +15007,7 @@
         <v>0.66841515583621913</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2018</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>0.66350773788692785</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2019</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>0.6615433638589453</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2020</v>
       </c>
@@ -15061,7 +15061,7 @@
         <v>0.66006155211410589</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2021</v>
       </c>
@@ -15079,7 +15079,7 @@
         <v>0.65222229330375292</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2022</v>
       </c>
@@ -15097,7 +15097,7 @@
         <v>0.65603112023999577</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2023</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>0.65354593619579027</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2024</v>
       </c>
@@ -15141,10 +15141,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{422104DD-44C3-4E39-9E8B-C1F675F90865}">
-  <dimension ref="A1:U18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U60"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -15206,1109 +15206,2117 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1850</v>
       </c>
       <c r="B2">
-        <v>0.57819235324859619</v>
+        <v>57.819235324859619</v>
       </c>
       <c r="C2">
-        <v>1.8606938421726227E-2</v>
+        <v>1.8606938421726227</v>
       </c>
       <c r="D2">
-        <v>6.6366635262966156E-2</v>
+        <v>6.6366635262966156</v>
       </c>
       <c r="E2">
-        <v>6.6211484372615814E-2</v>
+        <v>6.6211484372615814</v>
       </c>
       <c r="F2">
-        <v>7.6195657253265381E-2</v>
+        <v>7.6195657253265381</v>
       </c>
       <c r="G2">
-        <v>3.7025265395641327E-2</v>
+        <v>3.7025265395641327</v>
       </c>
       <c r="H2">
-        <v>1.2874718231614679E-4</v>
+        <v>1.2874718231614679E-2</v>
       </c>
       <c r="I2">
-        <v>8.7151936895679682E-5</v>
+        <v>8.7151936895679682E-3</v>
       </c>
       <c r="J2">
-        <v>1.20670220348984E-3</v>
+        <v>0.120670220348984</v>
       </c>
       <c r="K2">
-        <v>8.2089640200138092E-2</v>
+        <v>8.2089640200138092</v>
       </c>
       <c r="L2">
-        <v>1.9047979731112719E-3</v>
+        <v>0.19047979731112719</v>
       </c>
       <c r="M2">
-        <v>3.075890988111496E-2</v>
+        <v>3.075890988111496</v>
       </c>
       <c r="N2">
-        <v>5.5462522432208061E-3</v>
+        <v>0.55462522432208061</v>
       </c>
       <c r="O2">
-        <v>8.6249603191390634E-4</v>
+        <v>8.6249603191390634E-2</v>
       </c>
       <c r="P2">
-        <v>2.890142984688282E-2</v>
+        <v>2.890142984688282</v>
       </c>
       <c r="Q2">
-        <v>5.9155477210879326E-3</v>
+        <v>0.59155477210879326</v>
       </c>
       <c r="S2">
-        <f>E2+F2</f>
-        <v>0.1424071416258812</v>
+        <v>14.24071416258812</v>
       </c>
       <c r="T2">
-        <f>J2+K2</f>
-        <v>8.3296342403627932E-2</v>
+        <v>8.3296342403627932</v>
       </c>
       <c r="U2">
-        <f>P2+L2</f>
-        <v>3.0806227819994092E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>3.0806227819994092</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1860</v>
       </c>
       <c r="B3">
-        <v>0.46236312389373779</v>
+        <v>46.236312389373779</v>
       </c>
       <c r="C3">
-        <v>1.330214086920023E-2</v>
+        <v>1.330214086920023</v>
       </c>
       <c r="D3">
-        <v>6.0578044503927231E-2</v>
+        <v>6.0578044503927231</v>
       </c>
       <c r="E3">
-        <v>5.5885538458824158E-2</v>
+        <v>5.5885538458824158</v>
       </c>
       <c r="F3">
-        <v>6.8715214729309082E-2</v>
+        <v>6.8715214729309082</v>
       </c>
       <c r="G3">
-        <v>3.5700798034667969E-2</v>
+        <v>3.5700798034667969</v>
       </c>
       <c r="H3">
-        <v>2.4539860896766186E-4</v>
+        <v>2.4539860896766186E-2</v>
       </c>
       <c r="I3">
-        <v>2.4821929400786757E-4</v>
+        <v>2.4821929400786757E-2</v>
       </c>
       <c r="J3">
-        <v>2.2421223111450672E-3</v>
+        <v>0.22421223111450672</v>
       </c>
       <c r="K3">
-        <v>9.1080650687217712E-2</v>
+        <v>9.1080650687217712</v>
       </c>
       <c r="L3">
-        <v>2.7807143051177263E-3</v>
+        <v>0.27807143051177263</v>
       </c>
       <c r="M3">
-        <v>2.5524120777845383E-2</v>
+        <v>2.5524120777845383</v>
       </c>
       <c r="N3">
-        <v>0.13383015990257263</v>
+        <v>13.383015990257263</v>
       </c>
       <c r="O3">
-        <v>1.0706024477258325E-3</v>
+        <v>0.10706024477258325</v>
       </c>
       <c r="P3">
-        <v>4.031604528427124E-2</v>
+        <v>4.031604528427124</v>
       </c>
       <c r="Q3">
-        <v>6.1171012930572033E-3</v>
+        <v>0.61171012930572033</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S18" si="0">E3+F3</f>
-        <v>0.12460075318813324</v>
+        <v>12.460075318813324</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T18" si="1">J3+K3</f>
-        <v>9.332277299836278E-2</v>
+        <v>9.332277299836278</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U18" si="2">P3+L3</f>
-        <v>4.3096759589388967E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>4.3096759589388967</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1870</v>
       </c>
       <c r="B4">
-        <v>0.5239112377166748</v>
+        <v>52.39112377166748</v>
       </c>
       <c r="C4">
-        <v>1.5368103981018066E-2</v>
+        <v>1.5368103981018066</v>
       </c>
       <c r="D4">
-        <v>5.4915633052587509E-2</v>
+        <v>5.4915633052587509</v>
       </c>
       <c r="E4">
-        <v>5.6007653474807739E-2</v>
+        <v>5.6007653474807739</v>
       </c>
       <c r="F4">
-        <v>6.2792673707008362E-2</v>
+        <v>6.2792673707008362</v>
       </c>
       <c r="G4">
-        <v>4.4387795031070709E-2</v>
+        <v>4.4387795031070709</v>
       </c>
       <c r="H4">
-        <v>7.6498748967424035E-4</v>
+        <v>7.6498748967424035E-2</v>
       </c>
       <c r="I4">
-        <v>3.935467975679785E-4</v>
+        <v>3.935467975679785E-2</v>
       </c>
       <c r="J4">
-        <v>4.2736525647342205E-3</v>
+        <v>0.42736525647342205</v>
       </c>
       <c r="K4">
-        <v>7.3406219482421875E-2</v>
+        <v>7.3406219482421875</v>
       </c>
       <c r="L4">
-        <v>4.270549863576889E-3</v>
+        <v>0.4270549863576889</v>
       </c>
       <c r="M4">
-        <v>1.7843212932348251E-2</v>
+        <v>1.7843212932348251</v>
       </c>
       <c r="N4">
-        <v>0.10134658962488174</v>
+        <v>10.134658962488174</v>
       </c>
       <c r="O4">
-        <v>1.1670665116980672E-3</v>
+        <v>0.11670665116980672</v>
       </c>
       <c r="P4">
-        <v>3.1301464885473251E-2</v>
+        <v>3.1301464885473251</v>
       </c>
       <c r="Q4">
-        <v>7.8496057540178299E-3</v>
+        <v>0.78496057540178299</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
-        <v>0.1188003271818161</v>
+        <v>11.88003271818161</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
-        <v>7.7679872047156096E-2</v>
+        <v>7.7679872047156096</v>
       </c>
       <c r="U4">
-        <f t="shared" si="2"/>
-        <v>3.557201474905014E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>3.557201474905014</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1880</v>
       </c>
       <c r="B5">
-        <v>0.47245791554450989</v>
+        <v>47.245791554450989</v>
       </c>
       <c r="C5">
-        <v>1.7979327589273453E-2</v>
+        <v>1.7979327589273453</v>
       </c>
       <c r="D5">
-        <v>4.6275295317173004E-2</v>
+        <v>4.6275295317173004</v>
       </c>
       <c r="E5">
-        <v>6.1227142810821533E-2</v>
+        <v>6.1227142810821533</v>
       </c>
       <c r="F5">
-        <v>7.3320783674716949E-2</v>
+        <v>7.3320783674716949</v>
       </c>
       <c r="G5">
-        <v>4.5682802796363831E-2</v>
+        <v>4.5682802796363831</v>
       </c>
       <c r="H5">
-        <v>1.630279584787786E-3</v>
+        <v>0.1630279584787786</v>
       </c>
       <c r="I5">
-        <v>6.129500106908381E-4</v>
+        <v>6.129500106908381E-2</v>
       </c>
       <c r="J5">
-        <v>7.0726922713220119E-3</v>
+        <v>0.70726922713220119</v>
       </c>
       <c r="K5">
-        <v>8.4871970117092133E-2</v>
+        <v>8.4871970117092133</v>
       </c>
       <c r="L5">
-        <v>4.8382403329014778E-3</v>
+        <v>0.48382403329014778</v>
       </c>
       <c r="M5">
-        <v>1.7126139253377914E-2</v>
+        <v>1.7126139253377914</v>
       </c>
       <c r="N5">
-        <v>0.11800098419189453</v>
+        <v>11.800098419189453</v>
       </c>
       <c r="O5">
-        <v>1.6969897551462054E-3</v>
+        <v>0.16969897551462054</v>
       </c>
       <c r="P5">
-        <v>3.8222342729568481E-2</v>
+        <v>3.8222342729568481</v>
       </c>
       <c r="Q5">
-        <v>8.9841270819306374E-3</v>
+        <v>0.89841270819306374</v>
       </c>
       <c r="S5">
-        <f t="shared" si="0"/>
-        <v>0.13454792648553848</v>
+        <v>13.454792648553848</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
-        <v>9.1944662388414145E-2</v>
+        <v>9.1944662388414145</v>
       </c>
       <c r="U5">
-        <f t="shared" si="2"/>
-        <v>4.3060583062469959E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>4.3060583062469959</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1900</v>
       </c>
       <c r="B6">
-        <v>0.45154058933258057</v>
+        <v>45.154058933258057</v>
       </c>
       <c r="C6">
-        <v>2.3422442376613617E-2</v>
+        <v>2.3422442376613617</v>
       </c>
       <c r="D6">
-        <v>5.1770292222499847E-2</v>
+        <v>5.1770292222499847</v>
       </c>
       <c r="E6">
-        <v>5.9448372572660446E-2</v>
+        <v>5.9448372572660446</v>
       </c>
       <c r="F6">
-        <v>6.7088022828102112E-2</v>
+        <v>6.7088022828102112</v>
       </c>
       <c r="G6">
-        <v>5.8382533490657806E-2</v>
+        <v>5.8382533490657806</v>
       </c>
       <c r="H6">
-        <v>3.2795374281704426E-3</v>
+        <v>0.32795374281704426</v>
       </c>
       <c r="I6">
-        <v>6.5359199652448297E-4</v>
+        <v>6.5359199652448297E-2</v>
       </c>
       <c r="J6">
-        <v>7.4593108147382736E-3</v>
+        <v>0.74593108147382736</v>
       </c>
       <c r="K6">
-        <v>9.2042252421379089E-2</v>
+        <v>9.2042252421379089</v>
       </c>
       <c r="L6">
-        <v>1.3925276696681976E-2</v>
+        <v>1.3925276696681976</v>
       </c>
       <c r="M6">
-        <v>2.1757736802101135E-2</v>
+        <v>2.1757736802101135</v>
       </c>
       <c r="N6">
-        <v>9.8624572157859802E-2</v>
+        <v>9.8624572157859802</v>
       </c>
       <c r="O6">
-        <v>2.6226502377539873E-3</v>
+        <v>0.26226502377539873</v>
       </c>
       <c r="P6">
-        <v>3.9905402809381485E-2</v>
+        <v>3.9905402809381485</v>
       </c>
       <c r="Q6">
-        <v>8.0773690715432167E-3</v>
+        <v>0.80773690715432167</v>
       </c>
       <c r="S6">
-        <f t="shared" si="0"/>
-        <v>0.12653639540076256</v>
+        <v>12.653639540076256</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
-        <v>9.9501563236117363E-2</v>
+        <v>9.9501563236117363</v>
       </c>
       <c r="U6">
-        <f t="shared" si="2"/>
-        <v>5.3830679506063461E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>5.3830679506063461</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1910</v>
       </c>
       <c r="B7">
-        <v>0.36750513315200806</v>
+        <v>36.750513315200806</v>
       </c>
       <c r="C7">
-        <v>3.0998397618532181E-2</v>
+        <v>3.0998397618532181</v>
       </c>
       <c r="D7">
-        <v>5.9141885489225388E-2</v>
+        <v>5.9141885489225388</v>
       </c>
       <c r="E7">
-        <v>8.0444321036338806E-2</v>
+        <v>8.0444321036338806</v>
       </c>
       <c r="F7">
-        <v>7.9105034470558167E-2</v>
+        <v>7.9105034470558167</v>
       </c>
       <c r="G7">
-        <v>6.6540814936161041E-2</v>
+        <v>6.6540814936161041</v>
       </c>
       <c r="H7">
-        <v>5.9560942463576794E-3</v>
+        <v>0.59560942463576794</v>
       </c>
       <c r="I7">
-        <v>4.0072640404105186E-3</v>
+        <v>0.40072640404105186</v>
       </c>
       <c r="J7">
-        <v>9.3331532552838326E-3</v>
+        <v>0.93331532552838326</v>
       </c>
       <c r="K7">
-        <v>9.6236884593963623E-2</v>
+        <v>9.6236884593963623</v>
       </c>
       <c r="L7">
-        <v>1.500418595969677E-2</v>
+        <v>1.500418595969677</v>
       </c>
       <c r="M7">
-        <v>1.2927308678627014E-2</v>
+        <v>1.2927308678627014</v>
       </c>
       <c r="N7">
-        <v>0.1147225946187973</v>
+        <v>11.47225946187973</v>
       </c>
       <c r="O7">
-        <v>3.3035678789019585E-3</v>
+        <v>0.33035678789019585</v>
       </c>
       <c r="P7">
-        <v>4.2532637715339661E-2</v>
+        <v>4.2532637715339661</v>
       </c>
       <c r="Q7">
-        <v>1.2240718118846416E-2</v>
+        <v>1.2240718118846416</v>
       </c>
       <c r="S7">
-        <f t="shared" si="0"/>
-        <v>0.15954935550689697</v>
+        <v>15.954935550689697</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
-        <v>0.10557003784924746</v>
+        <v>10.557003784924746</v>
       </c>
       <c r="U7">
-        <f t="shared" si="2"/>
-        <v>5.753682367503643E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>5.753682367503643</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1920</v>
       </c>
       <c r="B8">
-        <v>0.32173064351081848</v>
+        <v>32.173064351081848</v>
       </c>
       <c r="C8">
-        <v>3.2925017178058624E-2</v>
+        <v>3.2925017178058624</v>
       </c>
       <c r="D8">
-        <v>5.1806323230266571E-2</v>
+        <v>5.1806323230266571</v>
       </c>
       <c r="E8">
-        <v>9.8316080868244171E-2</v>
+        <v>9.8316080868244171</v>
       </c>
       <c r="F8">
-        <v>9.7547240555286407E-2</v>
+        <v>9.7547240555286407</v>
       </c>
       <c r="G8">
-        <v>7.5634211301803589E-2</v>
+        <v>7.5634211301803589</v>
       </c>
       <c r="H8">
-        <v>1.0371803306043148E-2</v>
+        <v>1.0371803306043148</v>
       </c>
       <c r="I8">
-        <v>4.0269680321216583E-3</v>
+        <v>0.40269680321216583</v>
       </c>
       <c r="J8">
-        <v>1.3802834786474705E-2</v>
+        <v>1.3802834786474705</v>
       </c>
       <c r="K8">
-        <v>9.443972259759903E-2</v>
+        <v>9.443972259759903</v>
       </c>
       <c r="L8">
-        <v>2.0439600571990013E-2</v>
+        <v>2.0439600571990013</v>
       </c>
       <c r="M8">
-        <v>2.2894890978932381E-2</v>
+        <v>2.2894890978932381</v>
       </c>
       <c r="N8">
-        <v>8.3103075623512268E-2</v>
+        <v>8.3103075623512268</v>
       </c>
       <c r="O8">
-        <v>3.9357887580990791E-3</v>
+        <v>0.39357887580990791</v>
       </c>
       <c r="P8">
-        <v>4.8322077840566635E-2</v>
+        <v>4.8322077840566635</v>
       </c>
       <c r="Q8">
-        <v>2.0703712478280067E-2</v>
+        <v>2.0703712478280067</v>
       </c>
       <c r="S8">
-        <f t="shared" si="0"/>
-        <v>0.19586332142353058</v>
+        <v>19.586332142353058</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
-        <v>0.10824255738407373</v>
+        <v>10.824255738407373</v>
       </c>
       <c r="U8">
-        <f t="shared" si="2"/>
-        <v>6.8761678412556648E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>6.8761678412556648</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1930</v>
       </c>
       <c r="B9">
-        <v>0.26041856408119202</v>
+        <v>26.041856408119202</v>
       </c>
       <c r="C9">
-        <v>2.6690635830163956E-2</v>
+        <v>2.6690635830163956</v>
       </c>
       <c r="D9">
-        <v>6.6922903060913086E-2</v>
+        <v>6.6922903060913086</v>
       </c>
       <c r="E9">
-        <v>9.0909384191036224E-2</v>
+        <v>9.0909384191036224</v>
       </c>
       <c r="F9">
-        <v>9.4584345817565918E-2</v>
+        <v>9.4584345817565918</v>
       </c>
       <c r="G9">
-        <v>6.0283765196800232E-2</v>
+        <v>6.0283765196800232</v>
       </c>
       <c r="H9">
-        <v>1.1499687097966671E-2</v>
+        <v>1.1499687097966671</v>
       </c>
       <c r="I9">
-        <v>8.6242742836475372E-3</v>
+        <v>0.86242742836475372</v>
       </c>
       <c r="J9">
-        <v>1.4092238619923592E-2</v>
+        <v>1.4092238619923592</v>
       </c>
       <c r="K9">
-        <v>0.11901605129241943</v>
+        <v>11.901605129241943</v>
       </c>
       <c r="L9">
-        <v>3.4756287932395935E-2</v>
+        <v>3.4756287932395935</v>
       </c>
       <c r="M9">
-        <v>2.8083931654691696E-2</v>
+        <v>2.8083931654691696</v>
       </c>
       <c r="N9">
-        <v>9.4482079148292542E-2</v>
+        <v>9.4482079148292542</v>
       </c>
       <c r="O9">
-        <v>6.8218023516237736E-3</v>
+        <v>0.68218023516237736</v>
       </c>
       <c r="P9">
-        <v>6.1411336064338684E-2</v>
+        <v>6.1411336064338684</v>
       </c>
       <c r="Q9">
-        <v>2.1402699872851372E-2</v>
+        <v>2.1402699872851372</v>
       </c>
       <c r="S9">
-        <f t="shared" si="0"/>
-        <v>0.18549373000860214</v>
+        <v>18.549373000860214</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
-        <v>0.13310828991234303</v>
+        <v>13.310828991234303</v>
       </c>
       <c r="U9">
-        <f t="shared" si="2"/>
-        <v>9.6167623996734619E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>9.6167623996734619</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1940</v>
       </c>
       <c r="B10">
-        <v>0.18229062855243683</v>
+        <v>18.229062855243683</v>
       </c>
       <c r="C10">
-        <v>1.9697362557053566E-2</v>
+        <v>1.9697362557053566</v>
       </c>
       <c r="D10">
-        <v>9.4518892467021942E-2</v>
+        <v>9.4518892467021942</v>
       </c>
       <c r="E10">
-        <v>0.11001147329807281</v>
+        <v>11.001147329807281</v>
       </c>
       <c r="F10">
-        <v>0.11810895800590515</v>
+        <v>11.810895800590515</v>
       </c>
       <c r="G10">
-        <v>4.4665057212114334E-2</v>
+        <v>4.4665057212114334</v>
       </c>
       <c r="H10">
-        <v>6.5637798979878426E-3</v>
+        <v>0.65637798979878426</v>
       </c>
       <c r="I10">
-        <v>1.2303708121180534E-2</v>
+        <v>1.2303708121180534</v>
       </c>
       <c r="J10">
-        <v>2.9304603114724159E-2</v>
+        <v>2.9304603114724159</v>
       </c>
       <c r="K10">
-        <v>0.13369114696979523</v>
+        <v>13.369114696979523</v>
       </c>
       <c r="L10">
-        <v>3.120991587638855E-2</v>
+        <v>3.120991587638855</v>
       </c>
       <c r="M10">
-        <v>1.64052564650774E-2</v>
+        <v>1.64052564650774</v>
       </c>
       <c r="N10">
-        <v>8.3095602691173553E-2</v>
+        <v>8.3095602691173553</v>
       </c>
       <c r="O10">
-        <v>9.7337039187550545E-3</v>
+        <v>0.97337039187550545</v>
       </c>
       <c r="P10">
-        <v>7.1212083101272583E-2</v>
+        <v>7.1212083101272583</v>
       </c>
       <c r="Q10">
-        <v>3.7187863141298294E-2</v>
+        <v>3.7187863141298294</v>
       </c>
       <c r="S10">
-        <f t="shared" si="0"/>
-        <v>0.22812043130397797</v>
+        <v>22.812043130397797</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
-        <v>0.16299575008451939</v>
+        <v>16.299575008451939</v>
       </c>
       <c r="U10">
-        <f t="shared" si="2"/>
-        <v>0.10242199897766113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>10.242199897766113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1950</v>
       </c>
       <c r="B11">
-        <v>0.12103493511676788</v>
+        <v>12.103493511676788</v>
       </c>
       <c r="C11">
-        <v>1.6683559864759445E-2</v>
+        <v>1.6683559864759445</v>
       </c>
       <c r="D11">
-        <v>6.3431844115257263E-2</v>
+        <v>6.3431844115257263</v>
       </c>
       <c r="E11">
-        <v>0.1389591246843338</v>
+        <v>13.89591246843338</v>
       </c>
       <c r="F11">
-        <v>0.12203006446361542</v>
+        <v>12.203006446361542</v>
       </c>
       <c r="G11">
-        <v>5.2343495190143585E-2</v>
+        <v>5.2343495190143585</v>
       </c>
       <c r="H11">
-        <v>1.0940729640424252E-2</v>
+        <v>1.0940729640424252</v>
       </c>
       <c r="I11">
-        <v>1.3794760219752789E-2</v>
+        <v>1.3794760219752789</v>
       </c>
       <c r="J11">
-        <v>3.5603180527687073E-2</v>
+        <v>3.5603180527687073</v>
       </c>
       <c r="K11">
-        <v>0.15295414626598358</v>
+        <v>15.295414626598358</v>
       </c>
       <c r="L11">
-        <v>3.2965157181024551E-2</v>
+        <v>3.2965157181024551</v>
       </c>
       <c r="M11">
-        <v>2.5370582938194275E-2</v>
+        <v>2.5370582938194275</v>
       </c>
       <c r="N11">
-        <v>6.2259558588266373E-2</v>
+        <v>6.2259558588266373</v>
       </c>
       <c r="O11">
-        <v>1.0016065090894699E-2</v>
+        <v>1.0016065090894699</v>
       </c>
       <c r="P11">
-        <v>8.1281282007694244E-2</v>
+        <v>8.1281282007694244</v>
       </c>
       <c r="Q11">
-        <v>6.0331474989652634E-2</v>
+        <v>6.0331474989652634</v>
       </c>
       <c r="S11">
-        <f t="shared" si="0"/>
-        <v>0.26098918914794922</v>
+        <v>26.098918914794922</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
-        <v>0.18855732679367065</v>
+        <v>18.855732679367065</v>
       </c>
       <c r="U11">
-        <f t="shared" si="2"/>
-        <v>0.1142464391887188</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>11.42464391887188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1960</v>
       </c>
       <c r="B12">
-        <v>6.7470505833625793E-2</v>
+        <v>6.7470505833625793</v>
       </c>
       <c r="C12">
-        <v>1.0702317580580711E-2</v>
+        <v>1.0702317580580711</v>
       </c>
       <c r="D12">
-        <v>6.4334221184253693E-2</v>
+        <v>6.4334221184253693</v>
       </c>
       <c r="E12">
-        <v>0.15754368901252747</v>
+        <v>15.754368901252747</v>
       </c>
       <c r="F12">
-        <v>0.11940539628267288</v>
+        <v>11.940539628267288</v>
       </c>
       <c r="G12">
-        <v>4.3109007179737091E-2</v>
+        <v>4.3109007179737091</v>
       </c>
       <c r="H12">
-        <v>1.1166774667799473E-2</v>
+        <v>1.1166774667799473</v>
       </c>
       <c r="I12">
-        <v>1.3662181794643402E-2</v>
+        <v>1.3662181794643402</v>
       </c>
       <c r="J12">
-        <v>3.4507248550653458E-2</v>
+        <v>3.4507248550653458</v>
       </c>
       <c r="K12">
-        <v>0.15042921900749207</v>
+        <v>15.042921900749207</v>
       </c>
       <c r="L12">
-        <v>4.1136864572763443E-2</v>
+        <v>4.1136864572763443</v>
       </c>
       <c r="M12">
-        <v>2.7486983686685562E-2</v>
+        <v>2.7486983686685562</v>
       </c>
       <c r="N12">
-        <v>6.0875993221998215E-2</v>
+        <v>6.0875993221998215</v>
       </c>
       <c r="O12">
-        <v>9.7899055108428001E-3</v>
+        <v>0.97899055108428001</v>
       </c>
       <c r="P12">
-        <v>0.11306651681661606</v>
+        <v>11.306651681661606</v>
       </c>
       <c r="Q12">
-        <v>7.5313173234462738E-2</v>
+        <v>7.5313173234462738</v>
       </c>
       <c r="S12">
-        <f t="shared" si="0"/>
-        <v>0.27694908529520035</v>
+        <v>27.694908529520035</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
-        <v>0.18493646755814552</v>
+        <v>18.493646755814552</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
-        <v>0.1542033813893795</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>15.42033813893795</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1970</v>
       </c>
       <c r="B13">
-        <v>3.6652974784374237E-2</v>
+        <v>3.6652974784374237</v>
       </c>
       <c r="C13">
-        <v>7.925461046397686E-3</v>
+        <v>0.7925461046397686</v>
       </c>
       <c r="D13">
-        <v>5.9898030012845993E-2</v>
+        <v>5.9898030012845993</v>
       </c>
       <c r="E13">
-        <v>0.15243518352508545</v>
+        <v>15.243518352508545</v>
       </c>
       <c r="F13">
-        <v>0.1013019010424614</v>
+        <v>10.13019010424614</v>
       </c>
       <c r="G13">
-        <v>3.9484277367591858E-2</v>
+        <v>3.9484277367591858</v>
       </c>
       <c r="H13">
-        <v>1.1714734137058258E-2</v>
+        <v>1.1714734137058258</v>
       </c>
       <c r="I13">
-        <v>1.2146854773163795E-2</v>
+        <v>1.2146854773163795</v>
       </c>
       <c r="J13">
-        <v>3.9192140102386475E-2</v>
+        <v>3.9192140102386475</v>
       </c>
       <c r="K13">
-        <v>0.15816961228847504</v>
+        <v>15.816961228847504</v>
       </c>
       <c r="L13">
-        <v>4.7563109546899796E-2</v>
+        <v>4.7563109546899796</v>
       </c>
       <c r="M13">
-        <v>3.4205708652734756E-2</v>
+        <v>3.4205708652734756</v>
       </c>
       <c r="N13">
-        <v>4.6918582171201706E-2</v>
+        <v>4.6918582171201706</v>
       </c>
       <c r="O13">
-        <v>1.0550442151725292E-2</v>
+        <v>1.0550442151725292</v>
       </c>
       <c r="P13">
-        <v>0.16520586609840393</v>
+        <v>16.520586609840393</v>
       </c>
       <c r="Q13">
-        <v>7.6635107398033142E-2</v>
+        <v>7.6635107398033142</v>
       </c>
       <c r="S13">
-        <f t="shared" si="0"/>
-        <v>0.25373708456754684</v>
+        <v>25.373708456754684</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
-        <v>0.19736175239086151</v>
+        <v>19.736175239086151</v>
       </c>
       <c r="U13">
-        <f t="shared" si="2"/>
-        <v>0.21276897564530373</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>21.276897564530373</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1980</v>
       </c>
       <c r="B14">
-        <v>2.9561722651124001E-2</v>
+        <v>2.9561722651124001</v>
       </c>
       <c r="C14">
-        <v>1.0341251268982887E-2</v>
+        <v>1.0341251268982887</v>
       </c>
       <c r="D14">
-        <v>6.2934592366218567E-2</v>
+        <v>6.2934592366218567</v>
       </c>
       <c r="E14">
-        <v>0.13973744213581085</v>
+        <v>13.973744213581085</v>
       </c>
       <c r="F14">
-        <v>8.386143296957016E-2</v>
+        <v>8.386143296957016</v>
       </c>
       <c r="G14">
-        <v>3.590518981218338E-2</v>
+        <v>3.590518981218338</v>
       </c>
       <c r="H14">
-        <v>1.1815852485597134E-2</v>
+        <v>1.1815852485597134</v>
       </c>
       <c r="I14">
-        <v>1.3367202132940292E-2</v>
+        <v>1.3367202132940292</v>
       </c>
       <c r="J14">
-        <v>4.0643796324729919E-2</v>
+        <v>4.0643796324729919</v>
       </c>
       <c r="K14">
-        <v>0.16143004596233368</v>
+        <v>16.143004596233368</v>
       </c>
       <c r="L14">
-        <v>5.7794339954853058E-2</v>
+        <v>5.7794339954853058</v>
       </c>
       <c r="M14">
-        <v>4.5313462615013123E-2</v>
+        <v>4.5313462615013123</v>
       </c>
       <c r="N14">
-        <v>3.1288277357816696E-2</v>
+        <v>3.1288277357816696</v>
       </c>
       <c r="O14">
-        <v>1.2636471539735794E-2</v>
+        <v>1.2636471539735794</v>
       </c>
       <c r="P14">
-        <v>0.18990395963191986</v>
+        <v>18.990395963191986</v>
       </c>
       <c r="Q14">
-        <v>7.3464952409267426E-2</v>
+        <v>7.3464952409267426</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
-        <v>0.22359887510538101</v>
+        <v>22.359887510538101</v>
       </c>
       <c r="T14">
-        <f t="shared" si="1"/>
-        <v>0.2020738422870636</v>
+        <v>20.20738422870636</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
-        <v>0.24769829958677292</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+        <v>24.769829958677292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>2.709398977458477E-2</v>
+        <v>2.709398977458477</v>
       </c>
       <c r="C15">
-        <v>6.2341289594769478E-3</v>
+        <v>0.62341289594769478</v>
       </c>
       <c r="D15">
-        <v>6.4949169754981995E-2</v>
+        <v>6.4949169754981995</v>
       </c>
       <c r="E15">
-        <v>0.10356214642524719</v>
+        <v>10.356214642524719</v>
       </c>
       <c r="F15">
-        <v>7.1662090718746185E-2</v>
+        <v>7.1662090718746185</v>
       </c>
       <c r="G15">
-        <v>3.6138772964477539E-2</v>
+        <v>3.6138772964477539</v>
       </c>
       <c r="H15">
-        <v>1.0066951625049114E-2</v>
+        <v>1.0066951625049114</v>
       </c>
       <c r="I15">
-        <v>1.2361481785774231E-2</v>
+        <v>1.2361481785774231</v>
       </c>
       <c r="J15">
-        <v>4.1844803839921951E-2</v>
+        <v>4.1844803839921951</v>
       </c>
       <c r="K15">
-        <v>0.17052461206912994</v>
+        <v>17.052461206912994</v>
       </c>
       <c r="L15">
-        <v>6.6453568637371063E-2</v>
+        <v>6.6453568637371063</v>
       </c>
       <c r="M15">
-        <v>6.38594850897789E-2</v>
+        <v>6.38594850897789</v>
       </c>
       <c r="N15">
-        <v>3.1807463616132736E-2</v>
+        <v>3.1807463616132736</v>
       </c>
       <c r="O15">
-        <v>1.782798208296299E-2</v>
+        <v>1.782798208296299</v>
       </c>
       <c r="P15">
-        <v>0.20878003537654877</v>
+        <v>20.878003537654877</v>
       </c>
       <c r="Q15">
-        <v>6.6833280026912689E-2</v>
+        <v>6.6833280026912689</v>
       </c>
       <c r="S15">
-        <f t="shared" si="0"/>
-        <v>0.17522423714399338</v>
+        <v>17.522423714399338</v>
       </c>
       <c r="T15">
-        <f t="shared" si="1"/>
-        <v>0.2123694159090519</v>
+        <v>21.23694159090519</v>
       </c>
       <c r="U15">
-        <f t="shared" si="2"/>
-        <v>0.27523360401391983</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+        <v>27.523360401391983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2000</v>
       </c>
       <c r="B16">
-        <v>2.2298421710729599E-2</v>
+        <v>2.2298421710729599</v>
       </c>
       <c r="C16">
-        <v>3.8227732293307781E-3</v>
+        <v>0.38227732293307781</v>
       </c>
       <c r="D16">
-        <v>6.8821869790554047E-2</v>
+        <v>6.8821869790554047</v>
       </c>
       <c r="E16">
-        <v>9.0753950178623199E-2</v>
+        <v>9.0753950178623199</v>
       </c>
       <c r="F16">
-        <v>5.5321387946605682E-2</v>
+        <v>5.5321387946605682</v>
       </c>
       <c r="G16">
-        <v>3.7760745733976364E-2</v>
+        <v>3.7760745733976364</v>
       </c>
       <c r="H16">
-        <v>1.0092579759657383E-2</v>
+        <v>1.0092579759657383</v>
       </c>
       <c r="I16">
-        <v>1.1465713381767273E-2</v>
+        <v>1.1465713381767273</v>
       </c>
       <c r="J16">
-        <v>3.4737590700387955E-2</v>
+        <v>3.4737590700387955</v>
       </c>
       <c r="K16">
-        <v>0.17260131239891052</v>
+        <v>17.260131239891052</v>
       </c>
       <c r="L16">
-        <v>6.4793244004249573E-2</v>
+        <v>6.4793244004249573</v>
       </c>
       <c r="M16">
-        <v>8.1543847918510437E-2</v>
+        <v>8.1543847918510437</v>
       </c>
       <c r="N16">
-        <v>2.8271254152059555E-2</v>
+        <v>2.8271254152059555</v>
       </c>
       <c r="O16">
-        <v>2.0292710512876511E-2</v>
+        <v>2.0292710512876511</v>
       </c>
       <c r="P16">
-        <v>0.23601913452148438</v>
+        <v>23.601913452148438</v>
       </c>
       <c r="Q16">
-        <v>6.1403464525938034E-2</v>
+        <v>6.1403464525938034</v>
       </c>
       <c r="S16">
-        <f t="shared" si="0"/>
-        <v>0.14607533812522888</v>
+        <v>14.607533812522888</v>
       </c>
       <c r="T16">
-        <f t="shared" si="1"/>
-        <v>0.20733890309929848</v>
+        <v>20.733890309929848</v>
       </c>
       <c r="U16">
-        <f t="shared" si="2"/>
-        <v>0.30081237852573395</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+        <v>30.081237852573395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2010</v>
       </c>
       <c r="B17">
-        <v>2.4275433272123337E-2</v>
+        <v>2.4275433272123337</v>
       </c>
       <c r="C17">
-        <v>4.947370383888483E-3</v>
+        <v>0.4947370383888483</v>
       </c>
       <c r="D17">
-        <v>7.142060250043869E-2</v>
+        <v>7.142060250043869</v>
       </c>
       <c r="E17">
-        <v>6.7522153258323669E-2</v>
+        <v>6.7522153258323669</v>
       </c>
       <c r="F17">
-        <v>4.1181407868862152E-2</v>
+        <v>4.1181407868862152</v>
       </c>
       <c r="G17">
-        <v>3.6563612520694733E-2</v>
+        <v>3.6563612520694733</v>
       </c>
       <c r="H17">
-        <v>7.5859185308218002E-3</v>
+        <v>0.75859185308218002</v>
       </c>
       <c r="I17">
-        <v>8.5738012567162514E-3</v>
+        <v>0.85738012567162514</v>
       </c>
       <c r="J17">
-        <v>2.7643453329801559E-2</v>
+        <v>2.7643453329801559</v>
       </c>
       <c r="K17">
-        <v>0.18230018019676208</v>
+        <v>18.230018019676208</v>
       </c>
       <c r="L17">
-        <v>6.3345029950141907E-2</v>
+        <v>6.3345029950141907</v>
       </c>
       <c r="M17">
-        <v>8.2804232835769653E-2</v>
+        <v>8.2804232835769653</v>
       </c>
       <c r="N17">
-        <v>3.1340442597866058E-2</v>
+        <v>3.1340442597866058</v>
       </c>
       <c r="O17">
-        <v>2.1403493359684944E-2</v>
+        <v>2.1403493359684944</v>
       </c>
       <c r="P17">
-        <v>0.26847359538078308</v>
+        <v>26.847359538078308</v>
       </c>
       <c r="Q17">
-        <v>6.0619253665208817E-2</v>
+        <v>6.0619253665208817</v>
       </c>
       <c r="S17">
-        <f t="shared" si="0"/>
-        <v>0.10870356112718582</v>
+        <v>10.870356112718582</v>
       </c>
       <c r="T17">
-        <f t="shared" si="1"/>
-        <v>0.20994363352656364</v>
+        <v>20.994363352656364</v>
       </c>
       <c r="U17">
-        <f t="shared" si="2"/>
-        <v>0.33181862533092499</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+        <v>33.181862533092499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2018</v>
       </c>
       <c r="B18">
-        <v>2.356322854757309E-2</v>
+        <v>2.356322854757309</v>
       </c>
       <c r="C18">
-        <v>4.8930537886917591E-3</v>
+        <v>0.48930537886917591</v>
       </c>
       <c r="D18">
-        <v>7.0103690028190613E-2</v>
+        <v>7.0103690028190613</v>
       </c>
       <c r="E18">
-        <v>6.3596576452255249E-2</v>
+        <v>6.3596576452255249</v>
       </c>
       <c r="F18">
-        <v>3.7530321627855301E-2</v>
+        <v>3.7530321627855301</v>
       </c>
       <c r="G18">
-        <v>4.4213514775037766E-2</v>
+        <v>4.4213514775037766</v>
       </c>
       <c r="H18">
-        <v>6.4241145737469196E-3</v>
+        <v>0.64241145737469196</v>
       </c>
       <c r="I18">
-        <v>8.133426308631897E-3</v>
+        <v>0.8133426308631897</v>
       </c>
       <c r="J18">
-        <v>2.4153711274266243E-2</v>
+        <v>2.4153711274266243</v>
       </c>
       <c r="K18">
-        <v>0.1790844053030014</v>
+        <v>17.90844053030014</v>
       </c>
       <c r="L18">
-        <v>6.3340753316879272E-2</v>
+        <v>6.3340753316879272</v>
       </c>
       <c r="M18">
-        <v>9.274851530790329E-2</v>
+        <v>9.274851530790329</v>
       </c>
       <c r="N18">
-        <v>3.0843567103147507E-2</v>
+        <v>3.0843567103147507</v>
       </c>
       <c r="O18">
-        <v>2.1704070270061493E-2</v>
+        <v>2.1704070270061493</v>
       </c>
       <c r="P18">
-        <v>0.2742430567741394</v>
+        <v>27.42430567741394</v>
       </c>
       <c r="Q18">
-        <v>5.5423945188522339E-2</v>
+        <v>5.5423945188522339</v>
       </c>
       <c r="S18">
-        <f t="shared" si="0"/>
-        <v>0.10112689808011055</v>
+        <v>10.112689808011055</v>
       </c>
       <c r="T18">
-        <f t="shared" si="1"/>
-        <v>0.20323811657726765</v>
+        <v>20.323811657726765</v>
       </c>
       <c r="U18">
-        <f t="shared" si="2"/>
-        <v>0.33758381009101868</v>
+        <v>33.758381009101868</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1850</v>
+      </c>
+      <c r="B44">
+        <v>57.819235324859619</v>
+      </c>
+      <c r="C44">
+        <v>1.8606938421726227</v>
+      </c>
+      <c r="D44">
+        <v>6.6366635262966156</v>
+      </c>
+      <c r="E44">
+        <v>6.6211484372615814</v>
+      </c>
+      <c r="F44">
+        <v>7.6195657253265381</v>
+      </c>
+      <c r="G44">
+        <v>3.7025265395641327</v>
+      </c>
+      <c r="H44">
+        <v>1.2874718231614679E-2</v>
+      </c>
+      <c r="I44">
+        <v>8.7151936895679682E-3</v>
+      </c>
+      <c r="J44">
+        <v>0.120670220348984</v>
+      </c>
+      <c r="K44">
+        <v>8.2089640200138092</v>
+      </c>
+      <c r="L44">
+        <v>0.19047979731112719</v>
+      </c>
+      <c r="M44">
+        <v>3.075890988111496</v>
+      </c>
+      <c r="N44">
+        <v>0.55462522432208061</v>
+      </c>
+      <c r="O44">
+        <v>8.6249603191390634E-2</v>
+      </c>
+      <c r="P44">
+        <v>2.890142984688282</v>
+      </c>
+      <c r="Q44">
+        <v>0.59155477210879326</v>
+      </c>
+      <c r="S44">
+        <v>14.24071416258812</v>
+      </c>
+      <c r="T44">
+        <v>8.3296342403627932</v>
+      </c>
+      <c r="U44">
+        <v>3.0806227819994092</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1860</v>
+      </c>
+      <c r="B45">
+        <v>46.236312389373779</v>
+      </c>
+      <c r="C45">
+        <v>1.330214086920023</v>
+      </c>
+      <c r="D45">
+        <v>6.0578044503927231</v>
+      </c>
+      <c r="E45">
+        <v>5.5885538458824158</v>
+      </c>
+      <c r="F45">
+        <v>6.8715214729309082</v>
+      </c>
+      <c r="G45">
+        <v>3.5700798034667969</v>
+      </c>
+      <c r="H45">
+        <v>2.4539860896766186E-2</v>
+      </c>
+      <c r="I45">
+        <v>2.4821929400786757E-2</v>
+      </c>
+      <c r="J45">
+        <v>0.22421223111450672</v>
+      </c>
+      <c r="K45">
+        <v>9.1080650687217712</v>
+      </c>
+      <c r="L45">
+        <v>0.27807143051177263</v>
+      </c>
+      <c r="M45">
+        <v>2.5524120777845383</v>
+      </c>
+      <c r="N45">
+        <v>13.383015990257263</v>
+      </c>
+      <c r="O45">
+        <v>0.10706024477258325</v>
+      </c>
+      <c r="P45">
+        <v>4.031604528427124</v>
+      </c>
+      <c r="Q45">
+        <v>0.61171012930572033</v>
+      </c>
+      <c r="S45">
+        <v>12.460075318813324</v>
+      </c>
+      <c r="T45">
+        <v>9.332277299836278</v>
+      </c>
+      <c r="U45">
+        <v>4.3096759589388967</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1870</v>
+      </c>
+      <c r="B46">
+        <v>52.39112377166748</v>
+      </c>
+      <c r="C46">
+        <v>1.5368103981018066</v>
+      </c>
+      <c r="D46">
+        <v>5.4915633052587509</v>
+      </c>
+      <c r="E46">
+        <v>5.6007653474807739</v>
+      </c>
+      <c r="F46">
+        <v>6.2792673707008362</v>
+      </c>
+      <c r="G46">
+        <v>4.4387795031070709</v>
+      </c>
+      <c r="H46">
+        <v>7.6498748967424035E-2</v>
+      </c>
+      <c r="I46">
+        <v>3.935467975679785E-2</v>
+      </c>
+      <c r="J46">
+        <v>0.42736525647342205</v>
+      </c>
+      <c r="K46">
+        <v>7.3406219482421875</v>
+      </c>
+      <c r="L46">
+        <v>0.4270549863576889</v>
+      </c>
+      <c r="M46">
+        <v>1.7843212932348251</v>
+      </c>
+      <c r="N46">
+        <v>10.134658962488174</v>
+      </c>
+      <c r="O46">
+        <v>0.11670665116980672</v>
+      </c>
+      <c r="P46">
+        <v>3.1301464885473251</v>
+      </c>
+      <c r="Q46">
+        <v>0.78496057540178299</v>
+      </c>
+      <c r="S46">
+        <v>11.88003271818161</v>
+      </c>
+      <c r="T46">
+        <v>7.7679872047156096</v>
+      </c>
+      <c r="U46">
+        <v>3.557201474905014</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1880</v>
+      </c>
+      <c r="B47">
+        <v>47.245791554450989</v>
+      </c>
+      <c r="C47">
+        <v>1.7979327589273453</v>
+      </c>
+      <c r="D47">
+        <v>4.6275295317173004</v>
+      </c>
+      <c r="E47">
+        <v>6.1227142810821533</v>
+      </c>
+      <c r="F47">
+        <v>7.3320783674716949</v>
+      </c>
+      <c r="G47">
+        <v>4.5682802796363831</v>
+      </c>
+      <c r="H47">
+        <v>0.1630279584787786</v>
+      </c>
+      <c r="I47">
+        <v>6.129500106908381E-2</v>
+      </c>
+      <c r="J47">
+        <v>0.70726922713220119</v>
+      </c>
+      <c r="K47">
+        <v>8.4871970117092133</v>
+      </c>
+      <c r="L47">
+        <v>0.48382403329014778</v>
+      </c>
+      <c r="M47">
+        <v>1.7126139253377914</v>
+      </c>
+      <c r="N47">
+        <v>11.800098419189453</v>
+      </c>
+      <c r="O47">
+        <v>0.16969897551462054</v>
+      </c>
+      <c r="P47">
+        <v>3.8222342729568481</v>
+      </c>
+      <c r="Q47">
+        <v>0.89841270819306374</v>
+      </c>
+      <c r="S47">
+        <v>13.454792648553848</v>
+      </c>
+      <c r="T47">
+        <v>9.1944662388414145</v>
+      </c>
+      <c r="U47">
+        <v>4.3060583062469959</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1900</v>
+      </c>
+      <c r="B48">
+        <v>45.154058933258057</v>
+      </c>
+      <c r="C48">
+        <v>2.3422442376613617</v>
+      </c>
+      <c r="D48">
+        <v>5.1770292222499847</v>
+      </c>
+      <c r="E48">
+        <v>5.9448372572660446</v>
+      </c>
+      <c r="F48">
+        <v>6.7088022828102112</v>
+      </c>
+      <c r="G48">
+        <v>5.8382533490657806</v>
+      </c>
+      <c r="H48">
+        <v>0.32795374281704426</v>
+      </c>
+      <c r="I48">
+        <v>6.5359199652448297E-2</v>
+      </c>
+      <c r="J48">
+        <v>0.74593108147382736</v>
+      </c>
+      <c r="K48">
+        <v>9.2042252421379089</v>
+      </c>
+      <c r="L48">
+        <v>1.3925276696681976</v>
+      </c>
+      <c r="M48">
+        <v>2.1757736802101135</v>
+      </c>
+      <c r="N48">
+        <v>9.8624572157859802</v>
+      </c>
+      <c r="O48">
+        <v>0.26226502377539873</v>
+      </c>
+      <c r="P48">
+        <v>3.9905402809381485</v>
+      </c>
+      <c r="Q48">
+        <v>0.80773690715432167</v>
+      </c>
+      <c r="S48">
+        <v>12.653639540076256</v>
+      </c>
+      <c r="T48">
+        <v>9.9501563236117363</v>
+      </c>
+      <c r="U48">
+        <v>5.3830679506063461</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>1910</v>
+      </c>
+      <c r="B49">
+        <v>36.750513315200806</v>
+      </c>
+      <c r="C49">
+        <v>3.0998397618532181</v>
+      </c>
+      <c r="D49">
+        <v>5.9141885489225388</v>
+      </c>
+      <c r="E49">
+        <v>8.0444321036338806</v>
+      </c>
+      <c r="F49">
+        <v>7.9105034470558167</v>
+      </c>
+      <c r="G49">
+        <v>6.6540814936161041</v>
+      </c>
+      <c r="H49">
+        <v>0.59560942463576794</v>
+      </c>
+      <c r="I49">
+        <v>0.40072640404105186</v>
+      </c>
+      <c r="J49">
+        <v>0.93331532552838326</v>
+      </c>
+      <c r="K49">
+        <v>9.6236884593963623</v>
+      </c>
+      <c r="L49">
+        <v>1.500418595969677</v>
+      </c>
+      <c r="M49">
+        <v>1.2927308678627014</v>
+      </c>
+      <c r="N49">
+        <v>11.47225946187973</v>
+      </c>
+      <c r="O49">
+        <v>0.33035678789019585</v>
+      </c>
+      <c r="P49">
+        <v>4.2532637715339661</v>
+      </c>
+      <c r="Q49">
+        <v>1.2240718118846416</v>
+      </c>
+      <c r="S49">
+        <v>15.954935550689697</v>
+      </c>
+      <c r="T49">
+        <v>10.557003784924746</v>
+      </c>
+      <c r="U49">
+        <v>5.753682367503643</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>1920</v>
+      </c>
+      <c r="B50">
+        <v>32.173064351081848</v>
+      </c>
+      <c r="C50">
+        <v>3.2925017178058624</v>
+      </c>
+      <c r="D50">
+        <v>5.1806323230266571</v>
+      </c>
+      <c r="E50">
+        <v>9.8316080868244171</v>
+      </c>
+      <c r="F50">
+        <v>9.7547240555286407</v>
+      </c>
+      <c r="G50">
+        <v>7.5634211301803589</v>
+      </c>
+      <c r="H50">
+        <v>1.0371803306043148</v>
+      </c>
+      <c r="I50">
+        <v>0.40269680321216583</v>
+      </c>
+      <c r="J50">
+        <v>1.3802834786474705</v>
+      </c>
+      <c r="K50">
+        <v>9.443972259759903</v>
+      </c>
+      <c r="L50">
+        <v>2.0439600571990013</v>
+      </c>
+      <c r="M50">
+        <v>2.2894890978932381</v>
+      </c>
+      <c r="N50">
+        <v>8.3103075623512268</v>
+      </c>
+      <c r="O50">
+        <v>0.39357887580990791</v>
+      </c>
+      <c r="P50">
+        <v>4.8322077840566635</v>
+      </c>
+      <c r="Q50">
+        <v>2.0703712478280067</v>
+      </c>
+      <c r="S50">
+        <v>19.586332142353058</v>
+      </c>
+      <c r="T50">
+        <v>10.824255738407373</v>
+      </c>
+      <c r="U50">
+        <v>6.8761678412556648</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1930</v>
+      </c>
+      <c r="B51">
+        <v>26.041856408119202</v>
+      </c>
+      <c r="C51">
+        <v>2.6690635830163956</v>
+      </c>
+      <c r="D51">
+        <v>6.6922903060913086</v>
+      </c>
+      <c r="E51">
+        <v>9.0909384191036224</v>
+      </c>
+      <c r="F51">
+        <v>9.4584345817565918</v>
+      </c>
+      <c r="G51">
+        <v>6.0283765196800232</v>
+      </c>
+      <c r="H51">
+        <v>1.1499687097966671</v>
+      </c>
+      <c r="I51">
+        <v>0.86242742836475372</v>
+      </c>
+      <c r="J51">
+        <v>1.4092238619923592</v>
+      </c>
+      <c r="K51">
+        <v>11.901605129241943</v>
+      </c>
+      <c r="L51">
+        <v>3.4756287932395935</v>
+      </c>
+      <c r="M51">
+        <v>2.8083931654691696</v>
+      </c>
+      <c r="N51">
+        <v>9.4482079148292542</v>
+      </c>
+      <c r="O51">
+        <v>0.68218023516237736</v>
+      </c>
+      <c r="P51">
+        <v>6.1411336064338684</v>
+      </c>
+      <c r="Q51">
+        <v>2.1402699872851372</v>
+      </c>
+      <c r="S51">
+        <v>18.549373000860214</v>
+      </c>
+      <c r="T51">
+        <v>13.310828991234303</v>
+      </c>
+      <c r="U51">
+        <v>9.6167623996734619</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>1940</v>
+      </c>
+      <c r="B52">
+        <v>18.229062855243683</v>
+      </c>
+      <c r="C52">
+        <v>1.9697362557053566</v>
+      </c>
+      <c r="D52">
+        <v>9.4518892467021942</v>
+      </c>
+      <c r="E52">
+        <v>11.001147329807281</v>
+      </c>
+      <c r="F52">
+        <v>11.810895800590515</v>
+      </c>
+      <c r="G52">
+        <v>4.4665057212114334</v>
+      </c>
+      <c r="H52">
+        <v>0.65637798979878426</v>
+      </c>
+      <c r="I52">
+        <v>1.2303708121180534</v>
+      </c>
+      <c r="J52">
+        <v>2.9304603114724159</v>
+      </c>
+      <c r="K52">
+        <v>13.369114696979523</v>
+      </c>
+      <c r="L52">
+        <v>3.120991587638855</v>
+      </c>
+      <c r="M52">
+        <v>1.64052564650774</v>
+      </c>
+      <c r="N52">
+        <v>8.3095602691173553</v>
+      </c>
+      <c r="O52">
+        <v>0.97337039187550545</v>
+      </c>
+      <c r="P52">
+        <v>7.1212083101272583</v>
+      </c>
+      <c r="Q52">
+        <v>3.7187863141298294</v>
+      </c>
+      <c r="S52">
+        <v>22.812043130397797</v>
+      </c>
+      <c r="T52">
+        <v>16.299575008451939</v>
+      </c>
+      <c r="U52">
+        <v>10.242199897766113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>1950</v>
+      </c>
+      <c r="B53">
+        <v>12.103493511676788</v>
+      </c>
+      <c r="C53">
+        <v>1.6683559864759445</v>
+      </c>
+      <c r="D53">
+        <v>6.3431844115257263</v>
+      </c>
+      <c r="E53">
+        <v>13.89591246843338</v>
+      </c>
+      <c r="F53">
+        <v>12.203006446361542</v>
+      </c>
+      <c r="G53">
+        <v>5.2343495190143585</v>
+      </c>
+      <c r="H53">
+        <v>1.0940729640424252</v>
+      </c>
+      <c r="I53">
+        <v>1.3794760219752789</v>
+      </c>
+      <c r="J53">
+        <v>3.5603180527687073</v>
+      </c>
+      <c r="K53">
+        <v>15.295414626598358</v>
+      </c>
+      <c r="L53">
+        <v>3.2965157181024551</v>
+      </c>
+      <c r="M53">
+        <v>2.5370582938194275</v>
+      </c>
+      <c r="N53">
+        <v>6.2259558588266373</v>
+      </c>
+      <c r="O53">
+        <v>1.0016065090894699</v>
+      </c>
+      <c r="P53">
+        <v>8.1281282007694244</v>
+      </c>
+      <c r="Q53">
+        <v>6.0331474989652634</v>
+      </c>
+      <c r="S53">
+        <v>26.098918914794922</v>
+      </c>
+      <c r="T53">
+        <v>18.855732679367065</v>
+      </c>
+      <c r="U53">
+        <v>11.42464391887188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>1960</v>
+      </c>
+      <c r="B54">
+        <v>6.7470505833625793</v>
+      </c>
+      <c r="C54">
+        <v>1.0702317580580711</v>
+      </c>
+      <c r="D54">
+        <v>6.4334221184253693</v>
+      </c>
+      <c r="E54">
+        <v>15.754368901252747</v>
+      </c>
+      <c r="F54">
+        <v>11.940539628267288</v>
+      </c>
+      <c r="G54">
+        <v>4.3109007179737091</v>
+      </c>
+      <c r="H54">
+        <v>1.1166774667799473</v>
+      </c>
+      <c r="I54">
+        <v>1.3662181794643402</v>
+      </c>
+      <c r="J54">
+        <v>3.4507248550653458</v>
+      </c>
+      <c r="K54">
+        <v>15.042921900749207</v>
+      </c>
+      <c r="L54">
+        <v>4.1136864572763443</v>
+      </c>
+      <c r="M54">
+        <v>2.7486983686685562</v>
+      </c>
+      <c r="N54">
+        <v>6.0875993221998215</v>
+      </c>
+      <c r="O54">
+        <v>0.97899055108428001</v>
+      </c>
+      <c r="P54">
+        <v>11.306651681661606</v>
+      </c>
+      <c r="Q54">
+        <v>7.5313173234462738</v>
+      </c>
+      <c r="S54">
+        <v>27.694908529520035</v>
+      </c>
+      <c r="T54">
+        <v>18.493646755814552</v>
+      </c>
+      <c r="U54">
+        <v>15.42033813893795</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>1970</v>
+      </c>
+      <c r="B55">
+        <v>3.6652974784374237</v>
+      </c>
+      <c r="C55">
+        <v>0.7925461046397686</v>
+      </c>
+      <c r="D55">
+        <v>5.9898030012845993</v>
+      </c>
+      <c r="E55">
+        <v>15.243518352508545</v>
+      </c>
+      <c r="F55">
+        <v>10.13019010424614</v>
+      </c>
+      <c r="G55">
+        <v>3.9484277367591858</v>
+      </c>
+      <c r="H55">
+        <v>1.1714734137058258</v>
+      </c>
+      <c r="I55">
+        <v>1.2146854773163795</v>
+      </c>
+      <c r="J55">
+        <v>3.9192140102386475</v>
+      </c>
+      <c r="K55">
+        <v>15.816961228847504</v>
+      </c>
+      <c r="L55">
+        <v>4.7563109546899796</v>
+      </c>
+      <c r="M55">
+        <v>3.4205708652734756</v>
+      </c>
+      <c r="N55">
+        <v>4.6918582171201706</v>
+      </c>
+      <c r="O55">
+        <v>1.0550442151725292</v>
+      </c>
+      <c r="P55">
+        <v>16.520586609840393</v>
+      </c>
+      <c r="Q55">
+        <v>7.6635107398033142</v>
+      </c>
+      <c r="S55">
+        <v>25.373708456754684</v>
+      </c>
+      <c r="T55">
+        <v>19.736175239086151</v>
+      </c>
+      <c r="U55">
+        <v>21.276897564530373</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>1980</v>
+      </c>
+      <c r="B56">
+        <v>2.9561722651124001</v>
+      </c>
+      <c r="C56">
+        <v>1.0341251268982887</v>
+      </c>
+      <c r="D56">
+        <v>6.2934592366218567</v>
+      </c>
+      <c r="E56">
+        <v>13.973744213581085</v>
+      </c>
+      <c r="F56">
+        <v>8.386143296957016</v>
+      </c>
+      <c r="G56">
+        <v>3.590518981218338</v>
+      </c>
+      <c r="H56">
+        <v>1.1815852485597134</v>
+      </c>
+      <c r="I56">
+        <v>1.3367202132940292</v>
+      </c>
+      <c r="J56">
+        <v>4.0643796324729919</v>
+      </c>
+      <c r="K56">
+        <v>16.143004596233368</v>
+      </c>
+      <c r="L56">
+        <v>5.7794339954853058</v>
+      </c>
+      <c r="M56">
+        <v>4.5313462615013123</v>
+      </c>
+      <c r="N56">
+        <v>3.1288277357816696</v>
+      </c>
+      <c r="O56">
+        <v>1.2636471539735794</v>
+      </c>
+      <c r="P56">
+        <v>18.990395963191986</v>
+      </c>
+      <c r="Q56">
+        <v>7.3464952409267426</v>
+      </c>
+      <c r="S56">
+        <v>22.359887510538101</v>
+      </c>
+      <c r="T56">
+        <v>20.20738422870636</v>
+      </c>
+      <c r="U56">
+        <v>24.769829958677292</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>1990</v>
+      </c>
+      <c r="B57">
+        <v>2.709398977458477</v>
+      </c>
+      <c r="C57">
+        <v>0.62341289594769478</v>
+      </c>
+      <c r="D57">
+        <v>6.4949169754981995</v>
+      </c>
+      <c r="E57">
+        <v>10.356214642524719</v>
+      </c>
+      <c r="F57">
+        <v>7.1662090718746185</v>
+      </c>
+      <c r="G57">
+        <v>3.6138772964477539</v>
+      </c>
+      <c r="H57">
+        <v>1.0066951625049114</v>
+      </c>
+      <c r="I57">
+        <v>1.2361481785774231</v>
+      </c>
+      <c r="J57">
+        <v>4.1844803839921951</v>
+      </c>
+      <c r="K57">
+        <v>17.052461206912994</v>
+      </c>
+      <c r="L57">
+        <v>6.6453568637371063</v>
+      </c>
+      <c r="M57">
+        <v>6.38594850897789</v>
+      </c>
+      <c r="N57">
+        <v>3.1807463616132736</v>
+      </c>
+      <c r="O57">
+        <v>1.782798208296299</v>
+      </c>
+      <c r="P57">
+        <v>20.878003537654877</v>
+      </c>
+      <c r="Q57">
+        <v>6.6833280026912689</v>
+      </c>
+      <c r="S57">
+        <v>17.522423714399338</v>
+      </c>
+      <c r="T57">
+        <v>21.23694159090519</v>
+      </c>
+      <c r="U57">
+        <v>27.523360401391983</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>2000</v>
+      </c>
+      <c r="B58">
+        <v>2.2298421710729599</v>
+      </c>
+      <c r="C58">
+        <v>0.38227732293307781</v>
+      </c>
+      <c r="D58">
+        <v>6.8821869790554047</v>
+      </c>
+      <c r="E58">
+        <v>9.0753950178623199</v>
+      </c>
+      <c r="F58">
+        <v>5.5321387946605682</v>
+      </c>
+      <c r="G58">
+        <v>3.7760745733976364</v>
+      </c>
+      <c r="H58">
+        <v>1.0092579759657383</v>
+      </c>
+      <c r="I58">
+        <v>1.1465713381767273</v>
+      </c>
+      <c r="J58">
+        <v>3.4737590700387955</v>
+      </c>
+      <c r="K58">
+        <v>17.260131239891052</v>
+      </c>
+      <c r="L58">
+        <v>6.4793244004249573</v>
+      </c>
+      <c r="M58">
+        <v>8.1543847918510437</v>
+      </c>
+      <c r="N58">
+        <v>2.8271254152059555</v>
+      </c>
+      <c r="O58">
+        <v>2.0292710512876511</v>
+      </c>
+      <c r="P58">
+        <v>23.601913452148438</v>
+      </c>
+      <c r="Q58">
+        <v>6.1403464525938034</v>
+      </c>
+      <c r="S58">
+        <v>14.607533812522888</v>
+      </c>
+      <c r="T58">
+        <v>20.733890309929848</v>
+      </c>
+      <c r="U58">
+        <v>30.081237852573395</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>2010</v>
+      </c>
+      <c r="B59">
+        <v>2.4275433272123337</v>
+      </c>
+      <c r="C59">
+        <v>0.4947370383888483</v>
+      </c>
+      <c r="D59">
+        <v>7.142060250043869</v>
+      </c>
+      <c r="E59">
+        <v>6.7522153258323669</v>
+      </c>
+      <c r="F59">
+        <v>4.1181407868862152</v>
+      </c>
+      <c r="G59">
+        <v>3.6563612520694733</v>
+      </c>
+      <c r="H59">
+        <v>0.75859185308218002</v>
+      </c>
+      <c r="I59">
+        <v>0.85738012567162514</v>
+      </c>
+      <c r="J59">
+        <v>2.7643453329801559</v>
+      </c>
+      <c r="K59">
+        <v>18.230018019676208</v>
+      </c>
+      <c r="L59">
+        <v>6.3345029950141907</v>
+      </c>
+      <c r="M59">
+        <v>8.2804232835769653</v>
+      </c>
+      <c r="N59">
+        <v>3.1340442597866058</v>
+      </c>
+      <c r="O59">
+        <v>2.1403493359684944</v>
+      </c>
+      <c r="P59">
+        <v>26.847359538078308</v>
+      </c>
+      <c r="Q59">
+        <v>6.0619253665208817</v>
+      </c>
+      <c r="S59">
+        <v>10.870356112718582</v>
+      </c>
+      <c r="T59">
+        <v>20.994363352656364</v>
+      </c>
+      <c r="U59">
+        <v>33.181862533092499</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>2018</v>
+      </c>
+      <c r="B60">
+        <v>2.356322854757309</v>
+      </c>
+      <c r="C60">
+        <v>0.48930537886917591</v>
+      </c>
+      <c r="D60">
+        <v>7.0103690028190613</v>
+      </c>
+      <c r="E60">
+        <v>6.3596576452255249</v>
+      </c>
+      <c r="F60">
+        <v>3.7530321627855301</v>
+      </c>
+      <c r="G60">
+        <v>4.4213514775037766</v>
+      </c>
+      <c r="H60">
+        <v>0.64241145737469196</v>
+      </c>
+      <c r="I60">
+        <v>0.8133426308631897</v>
+      </c>
+      <c r="J60">
+        <v>2.4153711274266243</v>
+      </c>
+      <c r="K60">
+        <v>17.90844053030014</v>
+      </c>
+      <c r="L60">
+        <v>6.3340753316879272</v>
+      </c>
+      <c r="M60">
+        <v>9.274851530790329</v>
+      </c>
+      <c r="N60">
+        <v>3.0843567103147507</v>
+      </c>
+      <c r="O60">
+        <v>2.1704070270061493</v>
+      </c>
+      <c r="P60">
+        <v>27.42430567741394</v>
+      </c>
+      <c r="Q60">
+        <v>5.5423945188522339</v>
+      </c>
+      <c r="S60">
+        <v>10.112689808011055</v>
+      </c>
+      <c r="T60">
+        <v>20.323811657726765</v>
+      </c>
+      <c r="U60">
+        <v>33.758381009101868</v>
       </c>
     </row>
   </sheetData>
@@ -16320,9 +17328,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{861FEF25-5B38-413F-9A1D-6C30B4126523}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -16333,7 +17341,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -16347,7 +17355,7 @@
         <v>0.14791175723075867</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -16361,7 +17369,7 @@
         <v>0.13787184655666351</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -16375,7 +17383,7 @@
         <v>9.5109015703201294E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -16389,7 +17397,7 @@
         <v>5.328156054019928E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -16403,7 +17411,7 @@
         <v>5.6266408413648605E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -16417,7 +17425,7 @@
         <v>7.1959123015403748E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -16431,7 +17439,7 @@
         <v>7.3789343237876892E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -16445,7 +17453,7 @@
         <v>9.1273970901966095E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -16459,7 +17467,7 @@
         <v>0.11411100625991821</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -16473,7 +17481,7 @@
         <v>7.5094625353813171E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -16487,7 +17495,7 @@
         <v>8.5678078234195709E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -16501,7 +17509,7 @@
         <v>7.1725137531757355E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -16515,7 +17523,7 @@
         <v>6.0633547604084015E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -16529,7 +17537,7 @@
         <v>4.743904247879982E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -16543,7 +17551,7 @@
         <v>4.6396549791097641E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>53</v>
       </c>
